--- a/nilai-nilai/gti-2026/GTI_MIK1624406_2025_2_E.xlsx
+++ b/nilai-nilai/gti-2026/GTI_MIK1624406_2025_2_E.xlsx
@@ -41,7 +41,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +51,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD7BE"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -75,6 +80,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="3" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="3" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -616,7 +625,7 @@
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
       <c r="G8" s="5" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="H8" s="3" t="n"/>
       <c r="I8" s="3" t="n">
@@ -657,7 +666,7 @@
       </c>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H9" s="3" t="n"/>
@@ -699,7 +708,7 @@
       </c>
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H10" s="3" t="n"/>
@@ -741,7 +750,7 @@
       </c>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H11" s="3" t="n"/>
@@ -783,7 +792,7 @@
       </c>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n"/>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H12" s="3" t="n"/>
@@ -825,7 +834,7 @@
       </c>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n"/>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H13" s="3" t="n"/>
@@ -868,7 +877,7 @@
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
       <c r="G14" s="5" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H14" s="3" t="n"/>
       <c r="I14" s="3" t="n">
@@ -909,7 +918,7 @@
       </c>
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n"/>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H15" s="3" t="n"/>
@@ -952,7 +961,7 @@
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n"/>
       <c r="G16" s="5" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="H16" s="3" t="n"/>
       <c r="I16" s="3" t="n">
@@ -993,7 +1002,7 @@
       </c>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
-      <c r="G17" s="5" t="n">
+      <c r="G17" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H17" s="3" t="n"/>
@@ -1036,7 +1045,7 @@
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
       <c r="G18" s="5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H18" s="3" t="n"/>
       <c r="I18" s="3" t="n">
@@ -1078,7 +1087,7 @@
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="n"/>
       <c r="G19" s="5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H19" s="3" t="n"/>
       <c r="I19" s="3" t="n">
@@ -1119,7 +1128,7 @@
       </c>
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="n"/>
-      <c r="G20" s="5" t="n">
+      <c r="G20" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H20" s="3" t="n"/>
@@ -1161,7 +1170,7 @@
       </c>
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n"/>
-      <c r="G21" s="5" t="n">
+      <c r="G21" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H21" s="3" t="n"/>
@@ -1203,7 +1212,7 @@
       </c>
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="n"/>
-      <c r="G22" s="5" t="n">
+      <c r="G22" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H22" s="3" t="n"/>
@@ -1246,7 +1255,7 @@
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="n"/>
       <c r="G23" s="5" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="H23" s="3" t="n"/>
       <c r="I23" s="3" t="n">
@@ -1287,7 +1296,7 @@
       </c>
       <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="n"/>
-      <c r="G24" s="5" t="n">
+      <c r="G24" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H24" s="3" t="n"/>
@@ -1329,7 +1338,7 @@
       </c>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="n"/>
-      <c r="G25" s="5" t="n">
+      <c r="G25" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H25" s="3" t="n"/>
@@ -1371,7 +1380,7 @@
       </c>
       <c r="E26" s="3" t="n"/>
       <c r="F26" s="3" t="n"/>
-      <c r="G26" s="5" t="n">
+      <c r="G26" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H26" s="3" t="n"/>
@@ -1413,7 +1422,7 @@
       </c>
       <c r="E27" s="3" t="n"/>
       <c r="F27" s="3" t="n"/>
-      <c r="G27" s="5" t="n">
+      <c r="G27" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H27" s="3" t="n"/>
@@ -1455,7 +1464,7 @@
       </c>
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="n"/>
-      <c r="G28" s="5" t="n">
+      <c r="G28" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H28" s="3" t="n"/>
@@ -1497,7 +1506,7 @@
       </c>
       <c r="E29" s="3" t="n"/>
       <c r="F29" s="3" t="n"/>
-      <c r="G29" s="5" t="n">
+      <c r="G29" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H29" s="3" t="n"/>
@@ -1539,7 +1548,7 @@
       </c>
       <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="n"/>
-      <c r="G30" s="5" t="n">
+      <c r="G30" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H30" s="3" t="n"/>
@@ -1581,7 +1590,7 @@
       </c>
       <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n"/>
-      <c r="G31" s="5" t="n">
+      <c r="G31" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H31" s="3" t="n"/>
@@ -1623,7 +1632,7 @@
       </c>
       <c r="E32" s="3" t="n"/>
       <c r="F32" s="3" t="n"/>
-      <c r="G32" s="5" t="n">
+      <c r="G32" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H32" s="3" t="n"/>
@@ -1665,7 +1674,7 @@
       </c>
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="3" t="n"/>
-      <c r="G33" s="5" t="n">
+      <c r="G33" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H33" s="3" t="n"/>
@@ -1707,7 +1716,7 @@
       </c>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n"/>
-      <c r="G34" s="5" t="n">
+      <c r="G34" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H34" s="3" t="n"/>
@@ -1749,7 +1758,7 @@
       </c>
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="n"/>
-      <c r="G35" s="5" t="n">
+      <c r="G35" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H35" s="3" t="n"/>
@@ -1792,7 +1801,7 @@
       <c r="E36" s="3" t="n"/>
       <c r="F36" s="3" t="n"/>
       <c r="G36" s="5" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H36" s="3" t="n"/>
       <c r="I36" s="3" t="n">
@@ -1834,7 +1843,7 @@
       <c r="E37" s="3" t="n"/>
       <c r="F37" s="3" t="n"/>
       <c r="G37" s="5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H37" s="3" t="n"/>
       <c r="I37" s="3" t="n">
@@ -1875,7 +1884,7 @@
       </c>
       <c r="E38" s="3" t="n"/>
       <c r="F38" s="3" t="n"/>
-      <c r="G38" s="5" t="n">
+      <c r="G38" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H38" s="3" t="n"/>
@@ -1917,7 +1926,7 @@
       </c>
       <c r="E39" s="3" t="n"/>
       <c r="F39" s="3" t="n"/>
-      <c r="G39" s="5" t="n">
+      <c r="G39" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H39" s="3" t="n"/>
@@ -1959,7 +1968,7 @@
       </c>
       <c r="E40" s="3" t="n"/>
       <c r="F40" s="3" t="n"/>
-      <c r="G40" s="5" t="n">
+      <c r="G40" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H40" s="3" t="n"/>
@@ -2001,7 +2010,7 @@
       </c>
       <c r="E41" s="3" t="n"/>
       <c r="F41" s="3" t="n"/>
-      <c r="G41" s="5" t="n">
+      <c r="G41" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H41" s="3" t="n"/>
@@ -2044,7 +2053,7 @@
       <c r="E42" s="3" t="n"/>
       <c r="F42" s="3" t="n"/>
       <c r="G42" s="5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H42" s="3" t="n"/>
       <c r="I42" s="3" t="n">
